--- a/отчеты Останкино (поставки)/Останкино_недогрузы/Луганск.xlsx
+++ b/отчеты Останкино (поставки)/Останкино_недогрузы/Луганск.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\отчеты Останкино (поставки)\Ost_orders\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\отчеты Останкино (поставки)\Останкино_недогрузы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42916E31-3B2C-4E18-9625-3B1D513756BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE69D0C3-8121-4DCB-BF11-A1345710B958}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1215,7 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1251,6 +1251,11 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1576,40 +1581,40 @@
       <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="M1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="11" t="s">
         <v>9</v>
       </c>
       <c r="O1" s="2" t="s">
@@ -2428,46 +2433,46 @@
     </row>
     <row r="2" spans="1:285" x14ac:dyDescent="0.25">
       <c r="C2" s="32">
-        <f>SUM(C3:C184)</f>
+        <f t="shared" ref="C2:BO2" si="0">SUM(C3:C184)</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E2" s="32">
+        <f>SUM(E3:E184)</f>
         <v>6167</v>
-      </c>
-      <c r="D2" s="32">
-        <f t="shared" ref="D2:BO2" si="0">SUM(D3:D184)</f>
-        <v>40</v>
-      </c>
-      <c r="E2" s="32">
-        <f t="shared" si="0"/>
-        <v>5632</v>
       </c>
       <c r="F2" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6537</v>
       </c>
       <c r="G2" s="32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-370</v>
       </c>
       <c r="H2" s="32">
         <f t="shared" si="0"/>
-        <v>6537</v>
-      </c>
-      <c r="I2" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J2" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K2" s="32">
+        <v>72.84</v>
+      </c>
+      <c r="I2" s="37">
+        <f>SUM(I3:I184)</f>
+        <v>40</v>
+      </c>
+      <c r="J2" s="38">
+        <f>SUM(J3:J184)</f>
+        <v>5632</v>
+      </c>
+      <c r="K2" s="38">
         <f t="shared" si="0"/>
         <v>5775</v>
       </c>
-      <c r="L2" s="32">
+      <c r="L2" s="38">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M2" s="32">
+        <v>-103</v>
+      </c>
+      <c r="M2" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3567,7 +3572,19 @@
       <c r="B3" s="24">
         <v>1</v>
       </c>
-      <c r="N3" s="25"/>
+      <c r="G3" s="31">
+        <f>E3-F3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35">
+        <f>I3+J3-K3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="29"/>
+      <c r="N3" s="35"/>
       <c r="P3" s="33"/>
       <c r="R3" s="31">
         <v>0</v>
@@ -3825,19 +3842,29 @@
       <c r="B4" s="24">
         <v>0.4</v>
       </c>
-      <c r="C4">
-        <v>72</v>
-      </c>
       <c r="E4">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="F4">
         <v>77</v>
       </c>
-      <c r="K4">
+      <c r="G4" s="31">
+        <f t="shared" ref="G4:G67" si="5">E4-F4</f>
+        <v>-5</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="36">
+        <v>72</v>
+      </c>
+      <c r="K4" s="36">
         <v>77</v>
       </c>
-      <c r="N4" s="25"/>
+      <c r="L4" s="35">
+        <f t="shared" ref="L4:L67" si="6">I4+J4-K4</f>
+        <v>-5</v>
+      </c>
+      <c r="M4" s="29"/>
+      <c r="N4" s="35"/>
       <c r="P4" s="33"/>
       <c r="R4" s="31">
         <v>0</v>
@@ -4318,19 +4345,29 @@
       <c r="B5" s="24">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>8</v>
       </c>
-      <c r="E5">
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="36">
         <v>4</v>
       </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="K5">
+      <c r="K5" s="36">
         <v>4</v>
       </c>
-      <c r="N5" s="25"/>
+      <c r="L5" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="29"/>
+      <c r="N5" s="35"/>
       <c r="P5" s="33"/>
       <c r="R5" s="31">
         <v>0</v>
@@ -4774,7 +4811,19 @@
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="N6" s="25"/>
+      <c r="G6" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="29"/>
+      <c r="N6" s="35"/>
       <c r="P6" s="33"/>
       <c r="R6" s="31">
         <v>0</v>
@@ -5069,7 +5118,19 @@
       <c r="B7" s="24">
         <v>1</v>
       </c>
-      <c r="N7" s="25"/>
+      <c r="G7" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="29"/>
+      <c r="N7" s="35"/>
       <c r="P7" s="33"/>
       <c r="R7" s="31">
         <v>0</v>
@@ -5364,19 +5425,29 @@
       <c r="B8" s="24">
         <v>0.25</v>
       </c>
-      <c r="C8">
-        <v>40</v>
-      </c>
       <c r="E8">
         <v>40</v>
       </c>
-      <c r="H8">
+      <c r="F8">
         <v>43</v>
       </c>
-      <c r="K8">
+      <c r="G8" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="36">
+        <v>40</v>
+      </c>
+      <c r="K8" s="36">
         <v>43</v>
       </c>
-      <c r="N8" s="25"/>
+      <c r="L8" s="35">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="M8" s="29"/>
+      <c r="N8" s="35"/>
       <c r="P8" s="33"/>
       <c r="R8" s="31">
         <v>0</v>
@@ -5537,19 +5608,29 @@
       <c r="B9" s="24">
         <v>1</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>126</v>
       </c>
-      <c r="E9">
+      <c r="F9">
+        <v>127</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="I9" s="25"/>
+      <c r="J9" s="36">
         <v>53</v>
       </c>
-      <c r="H9">
-        <v>127</v>
-      </c>
-      <c r="K9">
+      <c r="K9" s="36">
         <v>54</v>
       </c>
-      <c r="N9" s="28">
+      <c r="L9" s="35">
+        <f t="shared" si="6"/>
+        <v>-1</v>
+      </c>
+      <c r="M9" s="29"/>
+      <c r="N9" s="36">
         <v>221</v>
       </c>
       <c r="O9">
@@ -6156,7 +6237,19 @@
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="N10" s="25"/>
+      <c r="G10" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="29"/>
+      <c r="N10" s="35"/>
       <c r="P10" s="33"/>
       <c r="R10" s="31">
         <v>0</v>
@@ -6477,7 +6570,19 @@
       <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="N11" s="25"/>
+      <c r="G11" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="25"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="29"/>
+      <c r="N11" s="35"/>
       <c r="P11" s="33"/>
       <c r="R11" s="31">
         <v>0</v>
@@ -6842,19 +6947,29 @@
       <c r="B12" s="24">
         <v>1</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>183</v>
       </c>
-      <c r="E12">
+      <c r="F12">
+        <v>183</v>
+      </c>
+      <c r="G12" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="25"/>
+      <c r="J12" s="36">
         <v>182</v>
       </c>
-      <c r="H12">
-        <v>183</v>
-      </c>
-      <c r="K12">
+      <c r="K12" s="36">
         <v>182</v>
       </c>
-      <c r="N12" s="25"/>
+      <c r="L12" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="29"/>
+      <c r="N12" s="35"/>
       <c r="P12" s="33"/>
       <c r="R12" s="31">
         <v>0</v>
@@ -7432,19 +7547,29 @@
       <c r="B13" s="24">
         <v>1</v>
       </c>
-      <c r="C13">
-        <v>187</v>
-      </c>
       <c r="E13">
         <v>187</v>
       </c>
-      <c r="H13">
+      <c r="F13">
         <v>186</v>
       </c>
-      <c r="K13">
+      <c r="G13" s="31">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="36">
+        <v>187</v>
+      </c>
+      <c r="K13" s="36">
         <v>186</v>
       </c>
-      <c r="N13" s="28">
+      <c r="L13" s="35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M13" s="29"/>
+      <c r="N13" s="36">
         <v>112</v>
       </c>
       <c r="O13">
@@ -8066,19 +8191,29 @@
       <c r="B14" s="24">
         <v>0.25</v>
       </c>
-      <c r="C14">
-        <v>80</v>
-      </c>
       <c r="E14">
         <v>80</v>
       </c>
-      <c r="H14">
+      <c r="F14">
         <v>81</v>
       </c>
-      <c r="K14">
+      <c r="G14" s="31">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="36">
+        <v>80</v>
+      </c>
+      <c r="K14" s="36">
         <v>81</v>
       </c>
-      <c r="N14" s="25"/>
+      <c r="L14" s="35">
+        <f t="shared" si="6"/>
+        <v>-1</v>
+      </c>
+      <c r="M14" s="29"/>
+      <c r="N14" s="35"/>
       <c r="P14" s="33"/>
       <c r="R14" s="31">
         <v>0</v>
@@ -8537,7 +8672,19 @@
       <c r="B15" s="24">
         <v>0.15</v>
       </c>
-      <c r="N15" s="25"/>
+      <c r="G15" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="29"/>
+      <c r="N15" s="35"/>
       <c r="P15" s="33"/>
       <c r="R15" s="31">
         <v>0</v>
@@ -8832,7 +8979,19 @@
       <c r="B16" s="24">
         <v>0.15</v>
       </c>
-      <c r="N16" s="25"/>
+      <c r="G16" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="29"/>
+      <c r="N16" s="35"/>
       <c r="P16" s="33"/>
       <c r="R16" s="31">
         <v>0</v>
@@ -9127,7 +9286,19 @@
       <c r="B17" s="24">
         <v>0.15</v>
       </c>
-      <c r="N17" s="25"/>
+      <c r="G17" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="29"/>
+      <c r="N17" s="35"/>
       <c r="P17" s="33"/>
       <c r="R17" s="31">
         <v>0</v>
@@ -9422,7 +9593,19 @@
       <c r="B18" s="24">
         <v>1</v>
       </c>
-      <c r="N18" s="25"/>
+      <c r="G18" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="29"/>
+      <c r="N18" s="35"/>
       <c r="P18" s="33"/>
       <c r="R18" s="31">
         <v>0</v>
@@ -9717,7 +9900,19 @@
       <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="N19" s="25"/>
+      <c r="G19" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="29"/>
+      <c r="N19" s="35"/>
       <c r="P19" s="33"/>
       <c r="R19" s="31">
         <v>0</v>
@@ -10012,7 +10207,19 @@
       <c r="B20" s="24">
         <v>1</v>
       </c>
-      <c r="N20" s="25"/>
+      <c r="G20" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="25"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="29"/>
+      <c r="N20" s="35"/>
       <c r="P20" s="33"/>
       <c r="R20" s="31">
         <v>0</v>
@@ -10307,7 +10514,19 @@
       <c r="B21" s="24">
         <v>1</v>
       </c>
-      <c r="N21" s="25"/>
+      <c r="G21" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="29"/>
+      <c r="N21" s="35"/>
       <c r="P21" s="33"/>
       <c r="R21" s="31">
         <v>0</v>
@@ -10602,7 +10821,19 @@
       <c r="B22" s="24">
         <v>1</v>
       </c>
-      <c r="N22" s="25"/>
+      <c r="G22" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="29"/>
+      <c r="N22" s="35"/>
       <c r="P22" s="33"/>
       <c r="R22" s="31">
         <v>0</v>
@@ -10946,19 +11177,29 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>89</v>
-      </c>
       <c r="E23">
         <v>89</v>
       </c>
-      <c r="H23">
+      <c r="F23">
         <v>92</v>
       </c>
-      <c r="K23">
+      <c r="G23" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="36">
+        <v>89</v>
+      </c>
+      <c r="K23" s="36">
         <v>92</v>
       </c>
-      <c r="N23" s="25"/>
+      <c r="L23" s="35">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="M23" s="29"/>
+      <c r="N23" s="35"/>
       <c r="P23">
         <v>16</v>
       </c>
@@ -11482,19 +11723,29 @@
       <c r="B24" s="24">
         <v>0.25</v>
       </c>
-      <c r="C24">
-        <v>64</v>
-      </c>
       <c r="E24">
         <v>64</v>
       </c>
-      <c r="H24">
+      <c r="F24">
         <v>67</v>
       </c>
-      <c r="K24">
+      <c r="G24" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I24" s="25"/>
+      <c r="J24" s="36">
+        <v>64</v>
+      </c>
+      <c r="K24" s="36">
         <v>68</v>
       </c>
-      <c r="N24" s="25"/>
+      <c r="L24" s="35">
+        <f t="shared" si="6"/>
+        <v>-4</v>
+      </c>
+      <c r="M24" s="29"/>
+      <c r="N24" s="35"/>
       <c r="P24" s="33"/>
       <c r="R24" s="31">
         <v>0</v>
@@ -11997,16 +12248,30 @@
       <c r="B25" s="24">
         <v>0.4</v>
       </c>
-      <c r="E25">
+      <c r="F25">
+        <v>139</v>
+      </c>
+      <c r="G25" s="34">
+        <f t="shared" si="5"/>
+        <v>-139</v>
+      </c>
+      <c r="H25" s="31">
+        <f>-1*G25*B25</f>
+        <v>55.6</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="36">
         <v>138</v>
       </c>
-      <c r="H25">
+      <c r="K25" s="36">
         <v>139</v>
       </c>
-      <c r="K25">
-        <v>139</v>
-      </c>
-      <c r="N25" s="25"/>
+      <c r="L25" s="35">
+        <f t="shared" si="6"/>
+        <v>-1</v>
+      </c>
+      <c r="M25" s="29"/>
+      <c r="N25" s="35"/>
       <c r="P25" s="33"/>
       <c r="R25" s="31">
         <v>0</v>
@@ -12507,19 +12772,29 @@
       <c r="B26" s="24">
         <v>1</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>200</v>
       </c>
-      <c r="E26">
+      <c r="F26">
+        <v>195</v>
+      </c>
+      <c r="G26" s="31">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="I26" s="25"/>
+      <c r="J26" s="36">
         <v>85</v>
       </c>
-      <c r="H26">
-        <v>195</v>
-      </c>
-      <c r="K26">
+      <c r="K26" s="36">
         <v>84</v>
       </c>
-      <c r="N26" s="28">
+      <c r="L26" s="35">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="M26" s="29"/>
+      <c r="N26" s="36">
         <v>126</v>
       </c>
       <c r="O26">
@@ -13114,7 +13389,19 @@
       <c r="B27" s="24">
         <v>0.12</v>
       </c>
-      <c r="N27" s="25"/>
+      <c r="G27" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="25"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="29"/>
+      <c r="N27" s="35"/>
       <c r="P27" s="33"/>
       <c r="R27" s="31">
         <v>0</v>
@@ -13586,7 +13873,19 @@
       <c r="B28" s="24">
         <v>1</v>
       </c>
-      <c r="N28" s="25"/>
+      <c r="G28" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="29"/>
+      <c r="N28" s="35"/>
       <c r="P28" s="33"/>
       <c r="R28" s="31">
         <v>0</v>
@@ -13913,7 +14212,19 @@
       <c r="B29" s="24">
         <v>0.25</v>
       </c>
-      <c r="N29" s="25"/>
+      <c r="G29" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="25"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="29"/>
+      <c r="N29" s="35"/>
       <c r="P29" s="33"/>
       <c r="R29" s="31">
         <v>0</v>
@@ -14336,7 +14647,19 @@
       <c r="B30" s="24">
         <v>0.25</v>
       </c>
-      <c r="N30" s="25"/>
+      <c r="G30" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="25"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="29"/>
+      <c r="N30" s="35"/>
       <c r="P30" s="33"/>
       <c r="R30" s="31">
         <v>0</v>
@@ -14568,7 +14891,19 @@
       <c r="B31" s="24">
         <v>1</v>
       </c>
-      <c r="N31" s="25"/>
+      <c r="G31" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="25"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="29"/>
+      <c r="N31" s="35"/>
       <c r="P31" s="33"/>
       <c r="R31" s="31">
         <v>0</v>
@@ -14903,13 +15238,25 @@
       <c r="B32" s="24">
         <v>0.4</v>
       </c>
-      <c r="C32">
+      <c r="E32">
         <v>16</v>
       </c>
-      <c r="H32">
+      <c r="F32">
         <v>18</v>
       </c>
-      <c r="N32" s="25"/>
+      <c r="G32" s="31">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="I32" s="25"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="29"/>
+      <c r="N32" s="35"/>
       <c r="P32" s="33"/>
       <c r="R32" s="31">
         <v>0</v>
@@ -15394,7 +15741,19 @@
       <c r="B33" s="24">
         <v>1</v>
       </c>
-      <c r="N33" s="25"/>
+      <c r="G33" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="29"/>
+      <c r="N33" s="35"/>
       <c r="P33" s="33"/>
       <c r="R33" s="31">
         <v>0</v>
@@ -15689,19 +16048,29 @@
       <c r="B34" s="24">
         <v>1</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>121</v>
       </c>
-      <c r="E34">
+      <c r="F34">
+        <v>124</v>
+      </c>
+      <c r="G34" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I34" s="25"/>
+      <c r="J34" s="36">
         <v>53</v>
       </c>
-      <c r="H34">
-        <v>124</v>
-      </c>
-      <c r="K34">
+      <c r="K34" s="36">
         <v>53</v>
       </c>
-      <c r="N34" s="28">
+      <c r="L34" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="29"/>
+      <c r="N34" s="36">
         <v>81</v>
       </c>
       <c r="O34">
@@ -16314,19 +16683,29 @@
       <c r="B35" s="24">
         <v>0.22</v>
       </c>
-      <c r="C35">
-        <v>120</v>
-      </c>
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="H35">
+      <c r="F35">
         <v>121</v>
       </c>
-      <c r="K35">
+      <c r="G35" s="31">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="I35" s="25"/>
+      <c r="J35" s="36">
+        <v>120</v>
+      </c>
+      <c r="K35" s="36">
         <v>122</v>
       </c>
-      <c r="N35" s="25"/>
+      <c r="L35" s="35">
+        <f t="shared" si="6"/>
+        <v>-2</v>
+      </c>
+      <c r="M35" s="29"/>
+      <c r="N35" s="35"/>
       <c r="P35" s="33"/>
       <c r="R35" s="31">
         <v>0</v>
@@ -16787,7 +17166,19 @@
       <c r="B36" s="24">
         <v>1</v>
       </c>
-      <c r="N36" s="25"/>
+      <c r="G36" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="25"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="29"/>
+      <c r="N36" s="35"/>
       <c r="P36" s="33"/>
       <c r="R36" s="31">
         <v>0</v>
@@ -17082,7 +17473,19 @@
       <c r="B37" s="24">
         <v>0.4</v>
       </c>
-      <c r="N37" s="25"/>
+      <c r="G37" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="25"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="29"/>
+      <c r="N37" s="35"/>
       <c r="P37" s="33"/>
       <c r="R37" s="31">
         <v>0</v>
@@ -17431,7 +17834,19 @@
       <c r="B38" s="24">
         <v>1</v>
       </c>
-      <c r="N38" s="25"/>
+      <c r="G38" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="25"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="29"/>
+      <c r="N38" s="35"/>
       <c r="P38" s="33"/>
       <c r="R38" s="31">
         <v>0</v>
@@ -17726,7 +18141,19 @@
       <c r="B39" s="24">
         <v>1</v>
       </c>
-      <c r="N39" s="25"/>
+      <c r="G39" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="25"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="29"/>
+      <c r="N39" s="35"/>
       <c r="P39" s="33"/>
       <c r="R39" s="31">
         <v>0</v>
@@ -18021,7 +18448,19 @@
       <c r="B40" s="24">
         <v>0.4</v>
       </c>
-      <c r="N40" s="25"/>
+      <c r="G40" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I40" s="25"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="29"/>
+      <c r="N40" s="35"/>
       <c r="P40" s="33"/>
       <c r="R40" s="31">
         <v>0</v>
@@ -18316,7 +18755,19 @@
       <c r="B41" s="24">
         <v>0.33</v>
       </c>
-      <c r="N41" s="25"/>
+      <c r="G41" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="25"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="29"/>
+      <c r="N41" s="35"/>
       <c r="P41" s="33"/>
       <c r="R41" s="31">
         <v>0</v>
@@ -18640,7 +19091,19 @@
       <c r="B42" s="24">
         <v>1</v>
       </c>
-      <c r="N42" s="25"/>
+      <c r="G42" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="25"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="29"/>
+      <c r="N42" s="35"/>
       <c r="P42" s="33"/>
       <c r="R42" s="31">
         <v>0</v>
@@ -18943,7 +19406,19 @@
       <c r="B43" s="24">
         <v>1</v>
       </c>
-      <c r="N43" s="25"/>
+      <c r="G43" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="25"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="29"/>
+      <c r="N43" s="35"/>
       <c r="P43" s="33"/>
       <c r="R43" s="31">
         <v>0</v>
@@ -19238,7 +19713,19 @@
       <c r="B44" s="24">
         <v>0.36</v>
       </c>
-      <c r="N44" s="25"/>
+      <c r="G44" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="25"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="29"/>
+      <c r="N44" s="35"/>
       <c r="P44" s="33"/>
       <c r="R44" s="31">
         <v>0</v>
@@ -19533,7 +20020,19 @@
       <c r="B45" s="24">
         <v>0.3</v>
       </c>
-      <c r="N45" s="25"/>
+      <c r="G45" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="25"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="29"/>
+      <c r="N45" s="35"/>
       <c r="P45" s="33"/>
       <c r="R45" s="31">
         <v>0</v>
@@ -19857,7 +20356,19 @@
       <c r="B46" s="24">
         <v>0.35</v>
       </c>
-      <c r="N46" s="25"/>
+      <c r="G46" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="25"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="29"/>
+      <c r="N46" s="35"/>
       <c r="P46" s="33"/>
       <c r="R46" s="31">
         <v>0</v>
@@ -20152,7 +20663,19 @@
       <c r="B47" s="24">
         <v>1</v>
       </c>
-      <c r="N47" s="25"/>
+      <c r="G47" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="25"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="29"/>
+      <c r="N47" s="35"/>
       <c r="P47" s="33"/>
       <c r="R47" s="31">
         <v>0</v>
@@ -20447,7 +20970,19 @@
       <c r="B48" s="24">
         <v>0.09</v>
       </c>
-      <c r="N48" s="28">
+      <c r="G48" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="25"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="29"/>
+      <c r="N48" s="36">
         <v>150</v>
       </c>
       <c r="O48">
@@ -20745,19 +21280,29 @@
       <c r="B49" s="24">
         <v>0.15</v>
       </c>
-      <c r="C49">
+      <c r="E49">
         <v>32</v>
       </c>
-      <c r="E49">
+      <c r="F49">
+        <v>33</v>
+      </c>
+      <c r="G49" s="31">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="I49" s="25"/>
+      <c r="J49" s="36">
         <v>8</v>
       </c>
-      <c r="H49">
-        <v>33</v>
-      </c>
-      <c r="K49">
+      <c r="K49" s="36">
         <v>14</v>
       </c>
-      <c r="N49" s="28">
+      <c r="L49" s="35">
+        <f t="shared" si="6"/>
+        <v>-6</v>
+      </c>
+      <c r="M49" s="29"/>
+      <c r="N49" s="36">
         <v>72</v>
       </c>
       <c r="O49">
@@ -21044,19 +21589,33 @@
       <c r="B50" s="24">
         <v>0.09</v>
       </c>
-      <c r="C50">
+      <c r="E50">
         <v>90</v>
       </c>
-      <c r="E50">
+      <c r="F50">
+        <v>134</v>
+      </c>
+      <c r="G50" s="34">
+        <f t="shared" si="5"/>
+        <v>-44</v>
+      </c>
+      <c r="H50" s="31">
+        <f>-1*G50*B50</f>
+        <v>3.96</v>
+      </c>
+      <c r="I50" s="25"/>
+      <c r="J50" s="36">
         <v>130</v>
       </c>
-      <c r="H50">
+      <c r="K50" s="36">
         <v>134</v>
       </c>
-      <c r="K50">
-        <v>134</v>
-      </c>
-      <c r="N50" s="25"/>
+      <c r="L50" s="35">
+        <f t="shared" si="6"/>
+        <v>-4</v>
+      </c>
+      <c r="M50" s="29"/>
+      <c r="N50" s="35"/>
       <c r="P50" s="33"/>
       <c r="R50" s="31">
         <v>0</v>
@@ -21584,7 +22143,19 @@
       <c r="B51" s="24">
         <v>0.3</v>
       </c>
-      <c r="N51" s="25"/>
+      <c r="G51" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="25"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="29"/>
+      <c r="N51" s="35"/>
       <c r="P51" s="33"/>
       <c r="R51" s="31">
         <v>0</v>
@@ -21879,7 +22450,19 @@
       <c r="B52" s="24">
         <v>0.27</v>
       </c>
-      <c r="N52" s="25"/>
+      <c r="G52" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="25"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M52" s="29"/>
+      <c r="N52" s="35"/>
       <c r="P52" s="33"/>
       <c r="R52" s="31">
         <v>0</v>
@@ -22174,19 +22757,29 @@
       <c r="B53" s="24">
         <v>1</v>
       </c>
-      <c r="C53">
+      <c r="E53">
         <v>53</v>
       </c>
-      <c r="E53">
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53" s="31">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="I53" s="25"/>
+      <c r="J53" s="36">
         <v>19</v>
       </c>
-      <c r="H53">
-        <v>50</v>
-      </c>
-      <c r="K53">
+      <c r="K53" s="36">
         <v>21</v>
       </c>
-      <c r="N53" s="28">
+      <c r="L53" s="35">
+        <f t="shared" si="6"/>
+        <v>-2</v>
+      </c>
+      <c r="M53" s="29"/>
+      <c r="N53" s="36">
         <v>29</v>
       </c>
       <c r="O53">
@@ -22757,7 +23350,19 @@
       <c r="B54" s="24">
         <v>1</v>
       </c>
-      <c r="N54" s="25"/>
+      <c r="G54" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="25"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M54" s="29"/>
+      <c r="N54" s="35"/>
       <c r="P54" s="33"/>
       <c r="R54" s="31">
         <v>0</v>
@@ -23052,19 +23657,29 @@
       <c r="B55" s="24">
         <v>0.4</v>
       </c>
-      <c r="C55">
-        <v>48</v>
-      </c>
       <c r="E55">
         <v>48</v>
       </c>
-      <c r="H55">
+      <c r="F55">
         <v>51</v>
       </c>
-      <c r="K55">
+      <c r="G55" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I55" s="25"/>
+      <c r="J55" s="36">
+        <v>48</v>
+      </c>
+      <c r="K55" s="36">
         <v>52</v>
       </c>
-      <c r="N55" s="25"/>
+      <c r="L55" s="35">
+        <f t="shared" si="6"/>
+        <v>-4</v>
+      </c>
+      <c r="M55" s="29"/>
+      <c r="N55" s="35"/>
       <c r="P55" s="33"/>
       <c r="R55" s="31">
         <v>0</v>
@@ -23451,19 +24066,29 @@
       <c r="B56" s="24">
         <v>0.4</v>
       </c>
-      <c r="C56">
-        <v>88</v>
-      </c>
       <c r="E56">
         <v>88</v>
       </c>
-      <c r="H56">
+      <c r="F56">
         <v>94</v>
       </c>
-      <c r="K56">
+      <c r="G56" s="31">
+        <f t="shared" si="5"/>
+        <v>-6</v>
+      </c>
+      <c r="I56" s="25"/>
+      <c r="J56" s="36">
+        <v>88</v>
+      </c>
+      <c r="K56" s="36">
         <v>95</v>
       </c>
-      <c r="N56" s="25"/>
+      <c r="L56" s="35">
+        <f t="shared" si="6"/>
+        <v>-7</v>
+      </c>
+      <c r="M56" s="29"/>
+      <c r="N56" s="35"/>
       <c r="P56" s="33"/>
       <c r="R56" s="31">
         <v>0</v>
@@ -23739,7 +24364,19 @@
       <c r="B57" s="24">
         <v>0.5</v>
       </c>
-      <c r="N57" s="25"/>
+      <c r="G57" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="25"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="29"/>
+      <c r="N57" s="35"/>
       <c r="P57" s="33"/>
       <c r="R57" s="31">
         <v>0</v>
@@ -24034,19 +24671,29 @@
       <c r="B58" s="24">
         <v>0.4</v>
       </c>
-      <c r="C58">
-        <v>208</v>
-      </c>
       <c r="E58">
         <v>208</v>
       </c>
-      <c r="H58">
+      <c r="F58">
         <v>213</v>
       </c>
-      <c r="K58">
+      <c r="G58" s="31">
+        <f t="shared" si="5"/>
+        <v>-5</v>
+      </c>
+      <c r="I58" s="25"/>
+      <c r="J58" s="36">
+        <v>208</v>
+      </c>
+      <c r="K58" s="36">
         <v>213</v>
       </c>
-      <c r="N58" s="25"/>
+      <c r="L58" s="35">
+        <f t="shared" si="6"/>
+        <v>-5</v>
+      </c>
+      <c r="M58" s="29"/>
+      <c r="N58" s="35"/>
       <c r="P58" s="33"/>
       <c r="R58" s="31">
         <v>0</v>
@@ -24589,7 +25236,19 @@
       <c r="B59" s="24">
         <v>0.5</v>
       </c>
-      <c r="N59" s="25"/>
+      <c r="G59" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I59" s="25"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="29"/>
+      <c r="N59" s="35"/>
       <c r="P59" s="33"/>
       <c r="R59" s="31">
         <v>0</v>
@@ -24892,7 +25551,19 @@
       <c r="B60" s="24">
         <v>0.5</v>
       </c>
-      <c r="N60" s="25"/>
+      <c r="G60" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I60" s="25"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M60" s="29"/>
+      <c r="N60" s="35"/>
       <c r="P60" s="33"/>
       <c r="R60" s="31">
         <v>0</v>
@@ -25187,19 +25858,29 @@
       <c r="B61" s="24">
         <v>0.4</v>
       </c>
-      <c r="C61">
-        <v>104</v>
-      </c>
       <c r="E61">
         <v>104</v>
       </c>
-      <c r="H61">
+      <c r="F61">
         <v>110</v>
       </c>
-      <c r="K61">
+      <c r="G61" s="31">
+        <f t="shared" si="5"/>
+        <v>-6</v>
+      </c>
+      <c r="I61" s="25"/>
+      <c r="J61" s="36">
+        <v>104</v>
+      </c>
+      <c r="K61" s="36">
         <v>111</v>
       </c>
-      <c r="N61" s="25"/>
+      <c r="L61" s="35">
+        <f t="shared" si="6"/>
+        <v>-7</v>
+      </c>
+      <c r="M61" s="29"/>
+      <c r="N61" s="35"/>
       <c r="P61" s="33"/>
       <c r="R61" s="31">
         <v>0</v>
@@ -25721,19 +26402,29 @@
       <c r="B62" s="24">
         <v>0.4</v>
       </c>
-      <c r="C62">
-        <v>160</v>
-      </c>
       <c r="E62">
         <v>160</v>
       </c>
-      <c r="H62">
+      <c r="F62">
         <v>163</v>
       </c>
-      <c r="K62">
+      <c r="G62" s="31">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="I62" s="25"/>
+      <c r="J62" s="36">
+        <v>160</v>
+      </c>
+      <c r="K62" s="36">
         <v>162</v>
       </c>
-      <c r="N62" s="25"/>
+      <c r="L62" s="35">
+        <f t="shared" si="6"/>
+        <v>-2</v>
+      </c>
+      <c r="M62" s="29"/>
+      <c r="N62" s="35"/>
       <c r="P62" s="33"/>
       <c r="R62" s="31">
         <v>0</v>
@@ -26287,7 +26978,19 @@
       <c r="B63" s="16">
         <v>0.84</v>
       </c>
-      <c r="N63" s="25"/>
+      <c r="G63" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="25"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="29"/>
+      <c r="N63" s="35"/>
       <c r="P63" s="33"/>
       <c r="R63" s="31">
         <v>0</v>
@@ -26546,7 +27249,19 @@
       <c r="B64" s="24">
         <v>0.1</v>
       </c>
-      <c r="N64" s="28">
+      <c r="G64" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="25"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M64" s="29"/>
+      <c r="N64" s="36">
         <v>80</v>
       </c>
       <c r="O64">
@@ -27061,19 +27776,29 @@
       <c r="B65" s="24">
         <v>0.1</v>
       </c>
-      <c r="C65">
-        <v>294</v>
-      </c>
       <c r="E65">
         <v>294</v>
       </c>
-      <c r="H65">
+      <c r="F65">
         <v>303</v>
       </c>
-      <c r="K65">
+      <c r="G65" s="31">
+        <f t="shared" si="5"/>
+        <v>-9</v>
+      </c>
+      <c r="I65" s="25"/>
+      <c r="J65" s="36">
+        <v>294</v>
+      </c>
+      <c r="K65" s="36">
         <v>303</v>
       </c>
-      <c r="N65" s="25"/>
+      <c r="L65" s="35">
+        <f t="shared" si="6"/>
+        <v>-9</v>
+      </c>
+      <c r="M65" s="29"/>
+      <c r="N65" s="35"/>
       <c r="P65" s="33"/>
       <c r="R65" s="31">
         <v>0</v>
@@ -27585,19 +28310,29 @@
       <c r="B66" s="24">
         <v>0.1</v>
       </c>
-      <c r="C66">
-        <v>420</v>
-      </c>
       <c r="E66">
         <v>420</v>
       </c>
-      <c r="H66">
+      <c r="F66">
         <v>422</v>
       </c>
-      <c r="K66">
+      <c r="G66" s="31">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="I66" s="25"/>
+      <c r="J66" s="36">
+        <v>420</v>
+      </c>
+      <c r="K66" s="36">
         <v>423</v>
       </c>
-      <c r="N66" s="25"/>
+      <c r="L66" s="35">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="M66" s="29"/>
+      <c r="N66" s="35"/>
       <c r="P66" s="33"/>
       <c r="R66" s="31">
         <v>0</v>
@@ -28141,19 +28876,29 @@
       <c r="B67" s="24">
         <v>0.1</v>
       </c>
-      <c r="C67">
-        <v>80</v>
-      </c>
       <c r="E67">
         <v>80</v>
       </c>
-      <c r="H67">
+      <c r="F67">
         <v>80</v>
       </c>
-      <c r="K67">
+      <c r="G67" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="25"/>
+      <c r="J67" s="36">
         <v>80</v>
       </c>
-      <c r="N67" s="25"/>
+      <c r="K67" s="36">
+        <v>80</v>
+      </c>
+      <c r="L67" s="35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M67" s="29"/>
+      <c r="N67" s="35"/>
       <c r="P67" s="33"/>
       <c r="R67" s="31">
         <v>0</v>
@@ -28387,19 +29132,29 @@
       <c r="B68" s="24">
         <v>0.4</v>
       </c>
-      <c r="C68">
-        <v>132</v>
-      </c>
       <c r="E68">
         <v>132</v>
       </c>
-      <c r="H68">
+      <c r="F68">
         <v>132</v>
       </c>
-      <c r="K68">
+      <c r="G68" s="31">
+        <f t="shared" ref="G68:G131" si="7">E68-F68</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="25"/>
+      <c r="J68" s="36">
         <v>132</v>
       </c>
-      <c r="N68" s="25"/>
+      <c r="K68" s="36">
+        <v>132</v>
+      </c>
+      <c r="L68" s="35">
+        <f t="shared" ref="L68:L131" si="8">I68+J68-K68</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="29"/>
+      <c r="N68" s="35"/>
       <c r="P68" s="33"/>
       <c r="R68" s="31">
         <v>0</v>
@@ -28920,19 +29675,29 @@
       <c r="B69" s="24">
         <v>1</v>
       </c>
-      <c r="C69">
+      <c r="E69">
         <v>118</v>
       </c>
-      <c r="E69">
+      <c r="F69">
+        <v>119</v>
+      </c>
+      <c r="G69" s="31">
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+      <c r="I69" s="25"/>
+      <c r="J69" s="36">
         <v>121</v>
       </c>
-      <c r="H69">
-        <v>119</v>
-      </c>
-      <c r="K69">
+      <c r="K69" s="36">
         <v>120</v>
       </c>
-      <c r="N69" s="25"/>
+      <c r="L69" s="35">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="M69" s="29"/>
+      <c r="N69" s="35"/>
       <c r="P69" s="33"/>
       <c r="R69" s="31">
         <v>0</v>
@@ -29401,19 +30166,29 @@
       <c r="B70" s="24">
         <v>1</v>
       </c>
-      <c r="C70">
+      <c r="E70">
         <v>81</v>
       </c>
-      <c r="E70">
+      <c r="F70">
+        <v>78</v>
+      </c>
+      <c r="G70" s="31">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="I70" s="25"/>
+      <c r="J70" s="36">
         <v>34</v>
       </c>
-      <c r="H70">
-        <v>78</v>
-      </c>
-      <c r="K70">
+      <c r="K70" s="36">
         <v>33</v>
       </c>
-      <c r="N70" s="25"/>
+      <c r="L70" s="35">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="M70" s="29"/>
+      <c r="N70" s="35"/>
       <c r="P70" s="33"/>
       <c r="R70" s="31">
         <v>0</v>
@@ -29982,19 +30757,29 @@
       <c r="B71" s="24">
         <v>1</v>
       </c>
-      <c r="C71">
+      <c r="E71">
         <v>19</v>
       </c>
-      <c r="E71">
+      <c r="F71">
+        <v>19</v>
+      </c>
+      <c r="G71" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="25"/>
+      <c r="J71" s="36">
         <v>6</v>
       </c>
-      <c r="H71">
-        <v>19</v>
-      </c>
-      <c r="K71">
+      <c r="K71" s="36">
         <v>8</v>
       </c>
-      <c r="N71" s="25"/>
+      <c r="L71" s="35">
+        <f t="shared" si="8"/>
+        <v>-2</v>
+      </c>
+      <c r="M71" s="29"/>
+      <c r="N71" s="35"/>
       <c r="P71" s="33"/>
       <c r="R71" s="31">
         <v>0</v>
@@ -30578,7 +31363,19 @@
       <c r="B72" s="24">
         <v>0.1</v>
       </c>
-      <c r="N72" s="25"/>
+      <c r="G72" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="25"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="35"/>
+      <c r="L72" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="29"/>
+      <c r="N72" s="35"/>
       <c r="P72" s="33"/>
       <c r="R72" s="31">
         <v>0</v>
@@ -30873,7 +31670,19 @@
       <c r="B73" s="24">
         <v>1</v>
       </c>
-      <c r="N73" s="25"/>
+      <c r="G73" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="25"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
+      <c r="L73" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="29"/>
+      <c r="N73" s="35"/>
       <c r="P73" s="33"/>
       <c r="R73" s="31">
         <v>0</v>
@@ -31168,7 +31977,19 @@
       <c r="B74" s="24">
         <v>0.09</v>
       </c>
-      <c r="N74" s="25"/>
+      <c r="G74" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="25"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="35"/>
+      <c r="L74" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M74" s="29"/>
+      <c r="N74" s="35"/>
       <c r="P74" s="33"/>
       <c r="R74" s="31">
         <v>0</v>
@@ -31571,7 +32392,19 @@
       <c r="B75" s="24">
         <v>1</v>
       </c>
-      <c r="N75" s="25"/>
+      <c r="G75" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="25"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="29"/>
+      <c r="N75" s="35"/>
       <c r="P75" s="33"/>
       <c r="R75" s="31">
         <v>0</v>
@@ -31866,7 +32699,19 @@
       <c r="B76" s="24">
         <v>1</v>
       </c>
-      <c r="N76" s="25"/>
+      <c r="G76" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="25"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="29"/>
+      <c r="N76" s="35"/>
       <c r="P76" s="33"/>
       <c r="R76" s="31">
         <v>0</v>
@@ -32161,16 +33006,30 @@
       <c r="B77" s="24">
         <v>0.35</v>
       </c>
-      <c r="E77">
+      <c r="F77">
         <v>16</v>
       </c>
-      <c r="H77">
+      <c r="G77" s="34">
+        <f t="shared" si="7"/>
+        <v>-16</v>
+      </c>
+      <c r="H77" s="31">
+        <f>-1*G77*B77</f>
+        <v>5.6</v>
+      </c>
+      <c r="I77" s="25"/>
+      <c r="J77" s="36">
         <v>16</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="36">
         <v>16</v>
       </c>
-      <c r="N77" s="25"/>
+      <c r="L77" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="29"/>
+      <c r="N77" s="35"/>
       <c r="P77" s="33"/>
       <c r="R77" s="31">
         <v>0</v>
@@ -32647,7 +33506,19 @@
       <c r="B78" s="24">
         <v>1</v>
       </c>
-      <c r="N78" s="25"/>
+      <c r="G78" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I78" s="25"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="35"/>
+      <c r="L78" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M78" s="29"/>
+      <c r="N78" s="35"/>
       <c r="P78" s="33"/>
       <c r="R78" s="31">
         <v>0</v>
@@ -32942,19 +33813,29 @@
       <c r="B79" s="24">
         <v>1</v>
       </c>
-      <c r="C79">
-        <v>124</v>
-      </c>
       <c r="E79">
         <v>124</v>
       </c>
-      <c r="H79">
+      <c r="F79">
         <v>121</v>
       </c>
-      <c r="K79">
+      <c r="G79" s="31">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="I79" s="25"/>
+      <c r="J79" s="36">
+        <v>124</v>
+      </c>
+      <c r="K79" s="36">
         <v>121</v>
       </c>
-      <c r="N79" s="28">
+      <c r="L79" s="35">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="M79" s="29"/>
+      <c r="N79" s="36">
         <v>47</v>
       </c>
       <c r="O79">
@@ -33491,7 +34372,19 @@
       <c r="B80" s="24">
         <v>0.4</v>
       </c>
-      <c r="N80" s="25"/>
+      <c r="G80" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I80" s="25"/>
+      <c r="J80" s="35"/>
+      <c r="K80" s="35"/>
+      <c r="L80" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M80" s="29"/>
+      <c r="N80" s="35"/>
       <c r="P80" s="33"/>
       <c r="R80" s="31">
         <v>0</v>
@@ -33845,19 +34738,29 @@
       <c r="B81" s="24">
         <v>0.3</v>
       </c>
-      <c r="C81">
+      <c r="E81">
         <v>48</v>
       </c>
-      <c r="E81">
+      <c r="F81">
+        <v>50</v>
+      </c>
+      <c r="G81" s="31">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+      <c r="I81" s="25"/>
+      <c r="J81" s="36">
         <v>16</v>
       </c>
-      <c r="H81">
-        <v>50</v>
-      </c>
-      <c r="K81">
+      <c r="K81" s="36">
         <v>22</v>
       </c>
-      <c r="N81" s="28">
+      <c r="L81" s="35">
+        <f t="shared" si="8"/>
+        <v>-6</v>
+      </c>
+      <c r="M81" s="29"/>
+      <c r="N81" s="36">
         <v>144</v>
       </c>
       <c r="O81">
@@ -34255,7 +35158,19 @@
       <c r="B82" s="24">
         <v>1</v>
       </c>
-      <c r="N82" s="25"/>
+      <c r="G82" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="25"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="35"/>
+      <c r="L82" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="29"/>
+      <c r="N82" s="35"/>
       <c r="P82" s="33"/>
       <c r="R82" s="31">
         <v>0</v>
@@ -34506,7 +35421,19 @@
       <c r="B83" s="24">
         <v>1</v>
       </c>
-      <c r="N83" s="25"/>
+      <c r="G83" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I83" s="25"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="35"/>
+      <c r="L83" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M83" s="29"/>
+      <c r="N83" s="35"/>
       <c r="P83" s="33"/>
       <c r="R83" s="31">
         <v>0</v>
@@ -34801,7 +35728,19 @@
       <c r="B84" s="24">
         <v>1</v>
       </c>
-      <c r="N84" s="28">
+      <c r="G84" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="25"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M84" s="29"/>
+      <c r="N84" s="36">
         <v>168</v>
       </c>
       <c r="O84">
@@ -35389,7 +36328,19 @@
       <c r="B85" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N85" s="25"/>
+      <c r="G85" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="25"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="29"/>
+      <c r="N85" s="35"/>
       <c r="P85" s="33"/>
       <c r="R85" s="31">
         <v>0</v>
@@ -35717,7 +36668,19 @@
       <c r="B86" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N86" s="25"/>
+      <c r="G86" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I86" s="25"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="35"/>
+      <c r="L86" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M86" s="29"/>
+      <c r="N86" s="35"/>
       <c r="P86" s="33"/>
       <c r="R86" s="31">
         <v>0</v>
@@ -36012,7 +36975,19 @@
       <c r="B87" s="24">
         <v>0.35</v>
       </c>
-      <c r="N87" s="25"/>
+      <c r="G87" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I87" s="25"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="35"/>
+      <c r="L87" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M87" s="29"/>
+      <c r="N87" s="35"/>
       <c r="P87" s="33"/>
       <c r="R87" s="31">
         <v>0</v>
@@ -36352,7 +37327,19 @@
       <c r="B88" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N88" s="25"/>
+      <c r="G88" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="25"/>
+      <c r="J88" s="35"/>
+      <c r="K88" s="35"/>
+      <c r="L88" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M88" s="29"/>
+      <c r="N88" s="35"/>
       <c r="P88" s="33"/>
       <c r="R88" s="31">
         <v>0</v>
@@ -36755,7 +37742,19 @@
       <c r="B89" s="24">
         <v>0.35</v>
       </c>
-      <c r="N89" s="25"/>
+      <c r="G89" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="25"/>
+      <c r="J89" s="35"/>
+      <c r="K89" s="35"/>
+      <c r="L89" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M89" s="29"/>
+      <c r="N89" s="35"/>
       <c r="P89" s="33"/>
       <c r="R89" s="31">
         <v>0</v>
@@ -37106,7 +38105,19 @@
       <c r="B90" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N90" s="25"/>
+      <c r="G90" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="25"/>
+      <c r="J90" s="35"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="29"/>
+      <c r="N90" s="35"/>
       <c r="P90" s="33"/>
       <c r="R90" s="31">
         <v>0</v>
@@ -37401,19 +38412,29 @@
       <c r="B91" s="24">
         <v>0.35</v>
       </c>
-      <c r="C91">
+      <c r="E91">
         <v>184</v>
       </c>
-      <c r="E91">
+      <c r="F91">
+        <v>188</v>
+      </c>
+      <c r="G91" s="31">
+        <f t="shared" si="7"/>
+        <v>-4</v>
+      </c>
+      <c r="I91" s="25"/>
+      <c r="J91" s="36">
         <v>80</v>
       </c>
-      <c r="H91">
-        <v>188</v>
-      </c>
-      <c r="K91">
+      <c r="K91" s="36">
         <v>80</v>
       </c>
-      <c r="N91" s="28">
+      <c r="L91" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M91" s="29"/>
+      <c r="N91" s="36">
         <v>72</v>
       </c>
       <c r="O91">
@@ -38026,7 +39047,19 @@
       <c r="B92" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N92" s="25"/>
+      <c r="G92" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I92" s="25"/>
+      <c r="J92" s="35"/>
+      <c r="K92" s="35"/>
+      <c r="L92" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M92" s="29"/>
+      <c r="N92" s="35"/>
       <c r="P92" s="33"/>
       <c r="R92" s="31">
         <v>0</v>
@@ -38424,19 +39457,29 @@
       <c r="B93" s="24">
         <v>0.41</v>
       </c>
-      <c r="C93">
-        <v>296</v>
-      </c>
       <c r="E93">
         <v>296</v>
       </c>
-      <c r="H93">
+      <c r="F93">
         <v>301</v>
       </c>
-      <c r="K93">
+      <c r="G93" s="31">
+        <f t="shared" si="7"/>
+        <v>-5</v>
+      </c>
+      <c r="I93" s="25"/>
+      <c r="J93" s="36">
+        <v>296</v>
+      </c>
+      <c r="K93" s="36">
         <v>301</v>
       </c>
-      <c r="N93" s="25"/>
+      <c r="L93" s="35">
+        <f t="shared" si="8"/>
+        <v>-5</v>
+      </c>
+      <c r="M93" s="29"/>
+      <c r="N93" s="35"/>
       <c r="P93" s="33"/>
       <c r="R93" s="31">
         <v>0</v>
@@ -39028,7 +40071,19 @@
       <c r="B94" s="24">
         <v>0.5</v>
       </c>
-      <c r="N94" s="25"/>
+      <c r="G94" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I94" s="25"/>
+      <c r="J94" s="35"/>
+      <c r="K94" s="35"/>
+      <c r="L94" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="29"/>
+      <c r="N94" s="35"/>
       <c r="P94" s="33"/>
       <c r="R94" s="31">
         <v>0</v>
@@ -39323,7 +40378,19 @@
       <c r="B95" s="24">
         <v>0.41</v>
       </c>
-      <c r="N95" s="25"/>
+      <c r="G95" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="25"/>
+      <c r="J95" s="35"/>
+      <c r="K95" s="35"/>
+      <c r="L95" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="29"/>
+      <c r="N95" s="35"/>
       <c r="P95" s="33"/>
       <c r="R95" s="31">
         <v>0</v>
@@ -39646,19 +40713,29 @@
       <c r="B96" s="24">
         <v>0.41</v>
       </c>
-      <c r="C96">
-        <v>120</v>
-      </c>
       <c r="E96">
         <v>120</v>
       </c>
-      <c r="H96">
+      <c r="F96">
         <v>128</v>
       </c>
-      <c r="K96">
+      <c r="G96" s="31">
+        <f t="shared" si="7"/>
+        <v>-8</v>
+      </c>
+      <c r="I96" s="25"/>
+      <c r="J96" s="36">
+        <v>120</v>
+      </c>
+      <c r="K96" s="36">
         <v>129</v>
       </c>
-      <c r="N96" s="25"/>
+      <c r="L96" s="35">
+        <f t="shared" si="8"/>
+        <v>-9</v>
+      </c>
+      <c r="M96" s="29"/>
+      <c r="N96" s="35"/>
       <c r="P96" s="33"/>
       <c r="R96" s="31">
         <v>0</v>
@@ -39937,7 +41014,19 @@
       <c r="B97" s="24">
         <v>0.41</v>
       </c>
-      <c r="N97" s="25"/>
+      <c r="G97" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I97" s="25"/>
+      <c r="J97" s="35"/>
+      <c r="K97" s="35"/>
+      <c r="L97" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M97" s="29"/>
+      <c r="N97" s="35"/>
       <c r="P97" s="33"/>
       <c r="R97" s="31">
         <v>0</v>
@@ -40254,7 +41343,19 @@
       <c r="B98" s="24">
         <v>0.5</v>
       </c>
-      <c r="N98" s="25"/>
+      <c r="G98" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="25"/>
+      <c r="J98" s="35"/>
+      <c r="K98" s="35"/>
+      <c r="L98" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="29"/>
+      <c r="N98" s="35"/>
       <c r="P98" s="33"/>
       <c r="R98" s="31">
         <v>0</v>
@@ -40549,7 +41650,19 @@
       <c r="B99" s="24">
         <v>0.41</v>
       </c>
-      <c r="N99" s="25"/>
+      <c r="G99" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I99" s="25"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="35"/>
+      <c r="L99" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="29"/>
+      <c r="N99" s="35"/>
       <c r="P99" s="33"/>
       <c r="R99" s="31">
         <v>0</v>
@@ -40844,7 +41957,19 @@
       <c r="B100" s="24">
         <v>0.4</v>
       </c>
-      <c r="N100" s="25"/>
+      <c r="G100" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="25"/>
+      <c r="J100" s="35"/>
+      <c r="K100" s="35"/>
+      <c r="L100" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="29"/>
+      <c r="N100" s="35"/>
       <c r="P100" s="33"/>
       <c r="R100" s="31">
         <v>0</v>
@@ -41139,7 +42264,19 @@
       <c r="B101" s="24">
         <v>1</v>
       </c>
-      <c r="N101" s="25"/>
+      <c r="G101" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I101" s="25"/>
+      <c r="J101" s="35"/>
+      <c r="K101" s="35"/>
+      <c r="L101" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="29"/>
+      <c r="N101" s="35"/>
       <c r="P101" s="33"/>
       <c r="R101" s="31">
         <v>0</v>
@@ -41434,7 +42571,19 @@
       <c r="B102" s="24">
         <v>0.4</v>
       </c>
-      <c r="N102" s="25"/>
+      <c r="G102" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="25"/>
+      <c r="J102" s="35"/>
+      <c r="K102" s="35"/>
+      <c r="L102" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="29"/>
+      <c r="N102" s="35"/>
       <c r="P102" s="33"/>
       <c r="R102" s="31">
         <v>0</v>
@@ -41851,7 +43000,19 @@
       <c r="B103" s="24">
         <v>1</v>
       </c>
-      <c r="N103" s="25"/>
+      <c r="G103" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I103" s="25"/>
+      <c r="J103" s="35"/>
+      <c r="K103" s="35"/>
+      <c r="L103" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="29"/>
+      <c r="N103" s="35"/>
       <c r="P103" s="33"/>
       <c r="R103" s="31">
         <v>0</v>
@@ -42146,7 +43307,19 @@
       <c r="B104" s="24">
         <v>0.41</v>
       </c>
-      <c r="N104" s="25"/>
+      <c r="G104" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="25"/>
+      <c r="J104" s="35"/>
+      <c r="K104" s="35"/>
+      <c r="L104" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M104" s="29"/>
+      <c r="N104" s="35"/>
       <c r="P104" s="33"/>
       <c r="R104" s="31">
         <v>0</v>
@@ -42531,7 +43704,19 @@
       <c r="B105" s="24">
         <v>1</v>
       </c>
-      <c r="N105" s="25"/>
+      <c r="G105" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="25"/>
+      <c r="J105" s="35"/>
+      <c r="K105" s="35"/>
+      <c r="L105" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="29"/>
+      <c r="N105" s="35"/>
       <c r="P105" s="33"/>
       <c r="R105" s="31">
         <v>0</v>
@@ -42826,7 +44011,19 @@
       <c r="B106" s="24">
         <v>0.36</v>
       </c>
-      <c r="N106" s="28">
+      <c r="G106" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="25"/>
+      <c r="J106" s="35"/>
+      <c r="K106" s="35"/>
+      <c r="L106" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="29"/>
+      <c r="N106" s="36">
         <v>54</v>
       </c>
       <c r="O106">
@@ -43378,7 +44575,19 @@
       <c r="B107" s="24">
         <v>1</v>
       </c>
-      <c r="N107" s="25"/>
+      <c r="G107" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="25"/>
+      <c r="J107" s="35"/>
+      <c r="K107" s="35"/>
+      <c r="L107" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="29"/>
+      <c r="N107" s="35"/>
       <c r="P107" s="33"/>
       <c r="R107" s="31">
         <v>0</v>
@@ -43673,7 +44882,19 @@
       <c r="B108" s="24">
         <v>0.41</v>
       </c>
-      <c r="N108" s="25"/>
+      <c r="G108" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I108" s="25"/>
+      <c r="J108" s="35"/>
+      <c r="K108" s="35"/>
+      <c r="L108" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M108" s="29"/>
+      <c r="N108" s="35"/>
       <c r="P108" s="33"/>
       <c r="R108" s="31">
         <v>0</v>
@@ -44138,7 +45359,19 @@
       <c r="B109" s="24">
         <v>1</v>
       </c>
-      <c r="N109" s="25"/>
+      <c r="G109" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="25"/>
+      <c r="J109" s="35"/>
+      <c r="K109" s="35"/>
+      <c r="L109" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="29"/>
+      <c r="N109" s="35"/>
       <c r="P109" s="33"/>
       <c r="R109" s="31">
         <v>0</v>
@@ -44433,7 +45666,19 @@
       <c r="B110" s="24">
         <v>0.41</v>
       </c>
-      <c r="N110" s="25"/>
+      <c r="G110" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I110" s="25"/>
+      <c r="J110" s="35"/>
+      <c r="K110" s="35"/>
+      <c r="L110" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="29"/>
+      <c r="N110" s="35"/>
       <c r="P110" s="33"/>
       <c r="R110" s="31">
         <v>0</v>
@@ -44887,7 +46132,19 @@
       <c r="B111" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N111" s="25"/>
+      <c r="G111" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I111" s="25"/>
+      <c r="J111" s="35"/>
+      <c r="K111" s="35"/>
+      <c r="L111" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M111" s="29"/>
+      <c r="N111" s="35"/>
       <c r="P111" s="33"/>
       <c r="R111" s="31">
         <v>0</v>
@@ -45244,7 +46501,19 @@
       <c r="B112" s="24">
         <v>0.35</v>
       </c>
-      <c r="N112" s="25"/>
+      <c r="G112" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I112" s="25"/>
+      <c r="J112" s="35"/>
+      <c r="K112" s="35"/>
+      <c r="L112" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M112" s="29"/>
+      <c r="N112" s="35"/>
       <c r="P112" s="33"/>
       <c r="R112" s="31">
         <v>0</v>
@@ -45539,7 +46808,19 @@
       <c r="B113" s="24">
         <v>0.4</v>
       </c>
-      <c r="N113" s="25"/>
+      <c r="G113" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I113" s="25"/>
+      <c r="J113" s="35"/>
+      <c r="K113" s="35"/>
+      <c r="L113" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M113" s="29"/>
+      <c r="N113" s="35"/>
       <c r="P113" s="33"/>
       <c r="R113" s="31">
         <v>0</v>
@@ -45861,7 +47142,19 @@
       <c r="B114" s="24">
         <v>0.16</v>
       </c>
-      <c r="N114" s="25"/>
+      <c r="G114" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I114" s="25"/>
+      <c r="J114" s="35"/>
+      <c r="K114" s="35"/>
+      <c r="L114" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M114" s="29"/>
+      <c r="N114" s="35"/>
       <c r="P114" s="33"/>
       <c r="R114" s="31">
         <v>0</v>
@@ -46156,7 +47449,19 @@
       <c r="B115" s="24">
         <v>0.5</v>
       </c>
-      <c r="N115" s="25"/>
+      <c r="G115" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I115" s="25"/>
+      <c r="J115" s="35"/>
+      <c r="K115" s="35"/>
+      <c r="L115" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M115" s="29"/>
+      <c r="N115" s="35"/>
       <c r="P115" s="33"/>
       <c r="R115" s="31">
         <v>0</v>
@@ -46451,19 +47756,29 @@
       <c r="B116" s="24">
         <v>0.33</v>
       </c>
-      <c r="C116">
-        <v>72</v>
-      </c>
       <c r="E116">
         <v>72</v>
       </c>
-      <c r="H116">
+      <c r="F116">
         <v>72</v>
       </c>
-      <c r="K116">
+      <c r="G116" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I116" s="25"/>
+      <c r="J116" s="36">
         <v>72</v>
       </c>
-      <c r="N116" s="25"/>
+      <c r="K116" s="36">
+        <v>72</v>
+      </c>
+      <c r="L116" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M116" s="29"/>
+      <c r="N116" s="35"/>
       <c r="P116" s="33"/>
       <c r="R116" s="31">
         <v>0</v>
@@ -46888,7 +48203,19 @@
       <c r="B117" s="24">
         <v>1</v>
       </c>
-      <c r="N117" s="25"/>
+      <c r="G117" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I117" s="25"/>
+      <c r="J117" s="35"/>
+      <c r="K117" s="35"/>
+      <c r="L117" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M117" s="29"/>
+      <c r="N117" s="35"/>
       <c r="P117" s="33"/>
       <c r="R117" s="31">
         <v>0</v>
@@ -47183,7 +48510,19 @@
       <c r="B118" s="24">
         <v>0.33</v>
       </c>
-      <c r="N118" s="25"/>
+      <c r="G118" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I118" s="25"/>
+      <c r="J118" s="35"/>
+      <c r="K118" s="35"/>
+      <c r="L118" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="29"/>
+      <c r="N118" s="35"/>
       <c r="P118" s="33"/>
       <c r="Q118">
         <v>16</v>
@@ -47633,7 +48972,19 @@
       <c r="B119" s="24">
         <v>1</v>
       </c>
-      <c r="N119" s="25"/>
+      <c r="G119" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I119" s="25"/>
+      <c r="J119" s="35"/>
+      <c r="K119" s="35"/>
+      <c r="L119" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M119" s="29"/>
+      <c r="N119" s="35"/>
       <c r="P119" s="33"/>
       <c r="R119" s="31">
         <v>0</v>
@@ -47928,19 +49279,29 @@
       <c r="B120" s="24">
         <v>0.33</v>
       </c>
-      <c r="C120">
+      <c r="E120">
         <v>72</v>
       </c>
-      <c r="E120">
+      <c r="F120">
+        <v>79</v>
+      </c>
+      <c r="G120" s="31">
+        <f t="shared" si="7"/>
+        <v>-7</v>
+      </c>
+      <c r="I120" s="25"/>
+      <c r="J120" s="36">
         <v>80</v>
       </c>
-      <c r="H120">
-        <v>79</v>
-      </c>
-      <c r="K120">
+      <c r="K120" s="36">
         <v>80</v>
       </c>
-      <c r="N120" s="25"/>
+      <c r="L120" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M120" s="29"/>
+      <c r="N120" s="35"/>
       <c r="P120" s="33"/>
       <c r="R120" s="31">
         <v>0</v>
@@ -48429,7 +49790,19 @@
       <c r="B121" s="24">
         <v>1</v>
       </c>
-      <c r="N121" s="25"/>
+      <c r="G121" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="25"/>
+      <c r="J121" s="35"/>
+      <c r="K121" s="35"/>
+      <c r="L121" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M121" s="29"/>
+      <c r="N121" s="35"/>
       <c r="P121" s="33"/>
       <c r="R121" s="31">
         <v>0</v>
@@ -48755,7 +50128,19 @@
       <c r="B122" s="24">
         <v>0.33</v>
       </c>
-      <c r="N122" s="25"/>
+      <c r="G122" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I122" s="25"/>
+      <c r="J122" s="35"/>
+      <c r="K122" s="35"/>
+      <c r="L122" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M122" s="29"/>
+      <c r="N122" s="35"/>
       <c r="P122" s="33"/>
       <c r="R122" s="31">
         <v>0</v>
@@ -49068,7 +50453,19 @@
       <c r="B123" s="24">
         <v>1</v>
       </c>
-      <c r="N123" s="25"/>
+      <c r="G123" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="25"/>
+      <c r="J123" s="35"/>
+      <c r="K123" s="35"/>
+      <c r="L123" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M123" s="29"/>
+      <c r="N123" s="35"/>
       <c r="P123" s="33"/>
       <c r="R123" s="31">
         <v>0</v>
@@ -49363,7 +50760,19 @@
       <c r="B124" s="24">
         <v>0.75</v>
       </c>
-      <c r="N124" s="25"/>
+      <c r="G124" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="25"/>
+      <c r="J124" s="35"/>
+      <c r="K124" s="35"/>
+      <c r="L124" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M124" s="29"/>
+      <c r="N124" s="35"/>
       <c r="P124" s="33"/>
       <c r="R124" s="31">
         <v>0</v>
@@ -49658,7 +51067,19 @@
       <c r="B125" s="24">
         <v>0.66</v>
       </c>
-      <c r="N125" s="25"/>
+      <c r="G125" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I125" s="25"/>
+      <c r="J125" s="35"/>
+      <c r="K125" s="35"/>
+      <c r="L125" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M125" s="29"/>
+      <c r="N125" s="35"/>
       <c r="P125" s="33"/>
       <c r="R125" s="31">
         <v>0</v>
@@ -49953,7 +51374,19 @@
       <c r="B126" s="24">
         <v>0.66</v>
       </c>
-      <c r="N126" s="25"/>
+      <c r="G126" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I126" s="25"/>
+      <c r="J126" s="35"/>
+      <c r="K126" s="35"/>
+      <c r="L126" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="29"/>
+      <c r="N126" s="35"/>
       <c r="P126" s="33"/>
       <c r="R126" s="31">
         <v>0</v>
@@ -50248,7 +51681,19 @@
       <c r="B127" s="24">
         <v>0.66</v>
       </c>
-      <c r="N127" s="25"/>
+      <c r="G127" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="25"/>
+      <c r="J127" s="35"/>
+      <c r="K127" s="35"/>
+      <c r="L127" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="29"/>
+      <c r="N127" s="35"/>
       <c r="P127" s="33"/>
       <c r="R127" s="31">
         <v>0</v>
@@ -50543,19 +51988,29 @@
       <c r="B128" s="24">
         <v>0.33</v>
       </c>
-      <c r="C128">
-        <v>40</v>
-      </c>
       <c r="E128">
         <v>40</v>
       </c>
-      <c r="H128">
+      <c r="F128">
         <v>40</v>
       </c>
-      <c r="K128">
+      <c r="G128" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I128" s="25"/>
+      <c r="J128" s="36">
         <v>40</v>
       </c>
-      <c r="N128" s="25"/>
+      <c r="K128" s="36">
+        <v>40</v>
+      </c>
+      <c r="L128" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M128" s="29"/>
+      <c r="N128" s="35"/>
       <c r="P128" s="33"/>
       <c r="R128" s="31">
         <v>0</v>
@@ -51036,7 +52491,19 @@
       <c r="B129" s="24">
         <v>0.36</v>
       </c>
-      <c r="N129" s="25"/>
+      <c r="G129" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I129" s="25"/>
+      <c r="J129" s="35"/>
+      <c r="K129" s="35"/>
+      <c r="L129" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M129" s="29"/>
+      <c r="N129" s="35"/>
       <c r="P129" s="33"/>
       <c r="R129" s="31">
         <v>0</v>
@@ -51499,7 +52966,19 @@
       <c r="B130" s="24">
         <v>0.15</v>
       </c>
-      <c r="N130" s="25"/>
+      <c r="G130" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="25"/>
+      <c r="J130" s="35"/>
+      <c r="K130" s="35"/>
+      <c r="L130" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M130" s="29"/>
+      <c r="N130" s="35"/>
       <c r="P130" s="33"/>
       <c r="R130" s="31">
         <v>0</v>
@@ -51794,7 +53273,19 @@
       <c r="B131" s="24">
         <v>0.15</v>
       </c>
-      <c r="N131" s="25"/>
+      <c r="G131" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="25"/>
+      <c r="J131" s="35"/>
+      <c r="K131" s="35"/>
+      <c r="L131" s="35">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M131" s="29"/>
+      <c r="N131" s="35"/>
       <c r="P131" s="33"/>
       <c r="R131" s="31">
         <v>0</v>
@@ -52089,7 +53580,19 @@
       <c r="B132" s="24">
         <v>0.15</v>
       </c>
-      <c r="N132" s="25"/>
+      <c r="G132" s="31">
+        <f t="shared" ref="G132:G184" si="9">E132-F132</f>
+        <v>0</v>
+      </c>
+      <c r="I132" s="25"/>
+      <c r="J132" s="35"/>
+      <c r="K132" s="35"/>
+      <c r="L132" s="35">
+        <f t="shared" ref="L132:L184" si="10">I132+J132-K132</f>
+        <v>0</v>
+      </c>
+      <c r="M132" s="29"/>
+      <c r="N132" s="35"/>
       <c r="P132" s="33"/>
       <c r="R132" s="31">
         <v>0</v>
@@ -52384,19 +53887,29 @@
       <c r="B133" s="24">
         <v>1</v>
       </c>
-      <c r="C133">
+      <c r="E133">
         <v>212</v>
       </c>
-      <c r="E133">
+      <c r="F133">
+        <v>217</v>
+      </c>
+      <c r="G133" s="31">
+        <f t="shared" si="9"/>
+        <v>-5</v>
+      </c>
+      <c r="I133" s="25"/>
+      <c r="J133" s="36">
         <v>219</v>
       </c>
-      <c r="H133">
-        <v>217</v>
-      </c>
-      <c r="K133">
+      <c r="K133" s="36">
         <v>218</v>
       </c>
-      <c r="N133" s="28">
+      <c r="L133" s="35">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M133" s="29"/>
+      <c r="N133" s="36">
         <v>119</v>
       </c>
       <c r="O133">
@@ -53012,13 +54525,25 @@
       <c r="B134" s="24">
         <v>1</v>
       </c>
-      <c r="C134">
+      <c r="E134">
         <v>5</v>
       </c>
-      <c r="H134">
+      <c r="F134">
         <v>4</v>
       </c>
-      <c r="N134" s="25"/>
+      <c r="G134" s="31">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="I134" s="25"/>
+      <c r="J134" s="35"/>
+      <c r="K134" s="35"/>
+      <c r="L134" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="29"/>
+      <c r="N134" s="35"/>
       <c r="P134" s="33"/>
       <c r="R134" s="31">
         <v>0</v>
@@ -53173,7 +54698,19 @@
       <c r="B135" s="24">
         <v>0.1</v>
       </c>
-      <c r="N135" s="25"/>
+      <c r="G135" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I135" s="25"/>
+      <c r="J135" s="35"/>
+      <c r="K135" s="35"/>
+      <c r="L135" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M135" s="29"/>
+      <c r="N135" s="35"/>
       <c r="P135" s="33"/>
       <c r="R135" s="31">
         <v>0</v>
@@ -53491,19 +55028,29 @@
       <c r="B136" s="24">
         <v>0.4</v>
       </c>
-      <c r="C136">
-        <v>60</v>
-      </c>
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="H136">
+      <c r="F136">
         <v>62</v>
       </c>
-      <c r="K136">
+      <c r="G136" s="31">
+        <f t="shared" si="9"/>
+        <v>-2</v>
+      </c>
+      <c r="I136" s="25"/>
+      <c r="J136" s="36">
+        <v>60</v>
+      </c>
+      <c r="K136" s="36">
         <v>62</v>
       </c>
-      <c r="N136" s="25"/>
+      <c r="L136" s="35">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="M136" s="29"/>
+      <c r="N136" s="35"/>
       <c r="P136" s="33"/>
       <c r="R136" s="31">
         <v>0</v>
@@ -53792,7 +55339,19 @@
       <c r="B137" s="24">
         <v>1</v>
       </c>
-      <c r="N137" s="25"/>
+      <c r="G137" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I137" s="25"/>
+      <c r="J137" s="35"/>
+      <c r="K137" s="35"/>
+      <c r="L137" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M137" s="29"/>
+      <c r="N137" s="35"/>
       <c r="P137" s="33"/>
       <c r="R137" s="31">
         <v>0</v>
@@ -54087,7 +55646,19 @@
       <c r="B138" s="24">
         <v>1</v>
       </c>
-      <c r="N138" s="25"/>
+      <c r="G138" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I138" s="25"/>
+      <c r="J138" s="35"/>
+      <c r="K138" s="35"/>
+      <c r="L138" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M138" s="29"/>
+      <c r="N138" s="35"/>
       <c r="P138" s="33"/>
       <c r="R138" s="31">
         <v>0</v>
@@ -54382,19 +55953,29 @@
       <c r="B139" s="24">
         <v>1</v>
       </c>
-      <c r="C139">
-        <v>6</v>
-      </c>
       <c r="E139">
         <v>6</v>
       </c>
-      <c r="H139">
+      <c r="F139">
         <v>10</v>
       </c>
-      <c r="K139">
+      <c r="G139" s="31">
+        <f t="shared" si="9"/>
+        <v>-4</v>
+      </c>
+      <c r="I139" s="25"/>
+      <c r="J139" s="36">
+        <v>6</v>
+      </c>
+      <c r="K139" s="36">
         <v>9</v>
       </c>
-      <c r="N139" s="25"/>
+      <c r="L139" s="35">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="M139" s="29"/>
+      <c r="N139" s="35"/>
       <c r="P139">
         <v>18</v>
       </c>
@@ -54779,7 +56360,19 @@
       <c r="B140" s="24">
         <v>1</v>
       </c>
-      <c r="N140" s="25"/>
+      <c r="G140" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I140" s="25"/>
+      <c r="J140" s="35"/>
+      <c r="K140" s="35"/>
+      <c r="L140" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M140" s="29"/>
+      <c r="N140" s="35"/>
       <c r="P140" s="33"/>
       <c r="R140" s="31">
         <v>0</v>
@@ -55074,7 +56667,19 @@
       <c r="B141" s="24">
         <v>1</v>
       </c>
-      <c r="N141" s="25"/>
+      <c r="G141" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I141" s="25"/>
+      <c r="J141" s="35"/>
+      <c r="K141" s="35"/>
+      <c r="L141" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M141" s="29"/>
+      <c r="N141" s="35"/>
       <c r="P141" s="33"/>
       <c r="R141" s="31">
         <v>0</v>
@@ -55314,7 +56919,19 @@
       <c r="B142" s="24">
         <v>1</v>
       </c>
-      <c r="N142" s="25"/>
+      <c r="G142" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I142" s="25"/>
+      <c r="J142" s="35"/>
+      <c r="K142" s="35"/>
+      <c r="L142" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M142" s="29"/>
+      <c r="N142" s="35"/>
       <c r="P142" s="33"/>
       <c r="R142" s="31">
         <v>0</v>
@@ -55547,7 +57164,19 @@
       <c r="B143" s="24">
         <v>1</v>
       </c>
-      <c r="N143" s="25"/>
+      <c r="G143" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I143" s="25"/>
+      <c r="J143" s="35"/>
+      <c r="K143" s="35"/>
+      <c r="L143" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M143" s="29"/>
+      <c r="N143" s="35"/>
       <c r="P143" s="33"/>
       <c r="R143" s="31">
         <v>0</v>
@@ -55777,7 +57406,19 @@
       <c r="B144" s="24">
         <v>0.4</v>
       </c>
-      <c r="N144" s="25"/>
+      <c r="G144" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I144" s="25"/>
+      <c r="J144" s="35"/>
+      <c r="K144" s="35"/>
+      <c r="L144" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M144" s="29"/>
+      <c r="N144" s="35"/>
       <c r="P144" s="33"/>
       <c r="R144" s="31">
         <v>0</v>
@@ -56025,7 +57666,19 @@
       <c r="B145" s="24">
         <v>0.41</v>
       </c>
-      <c r="N145" s="25"/>
+      <c r="G145" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I145" s="25"/>
+      <c r="J145" s="35"/>
+      <c r="K145" s="35"/>
+      <c r="L145" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M145" s="29"/>
+      <c r="N145" s="35"/>
       <c r="P145" s="33"/>
       <c r="R145" s="31">
         <v>0</v>
@@ -56320,7 +57973,19 @@
       <c r="B146" s="24">
         <v>0.33</v>
       </c>
-      <c r="N146" s="25"/>
+      <c r="G146" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I146" s="25"/>
+      <c r="J146" s="35"/>
+      <c r="K146" s="35"/>
+      <c r="L146" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M146" s="29"/>
+      <c r="N146" s="35"/>
       <c r="P146" s="33"/>
       <c r="R146" s="31">
         <v>0</v>
@@ -56653,7 +58318,19 @@
       <c r="B147" s="24">
         <v>0.3</v>
       </c>
-      <c r="N147" s="25"/>
+      <c r="G147" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I147" s="25"/>
+      <c r="J147" s="35"/>
+      <c r="K147" s="35"/>
+      <c r="L147" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M147" s="29"/>
+      <c r="N147" s="35"/>
       <c r="P147" s="33"/>
       <c r="R147" s="31">
         <v>0</v>
@@ -56972,7 +58649,19 @@
       <c r="B148" s="24">
         <v>1</v>
       </c>
-      <c r="N148" s="25"/>
+      <c r="G148" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I148" s="25"/>
+      <c r="J148" s="35"/>
+      <c r="K148" s="35"/>
+      <c r="L148" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M148" s="29"/>
+      <c r="N148" s="35"/>
       <c r="P148" s="33"/>
       <c r="R148" s="31">
         <v>0</v>
@@ -57287,7 +58976,19 @@
       <c r="B149" s="24">
         <v>1</v>
       </c>
-      <c r="N149" s="25"/>
+      <c r="G149" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I149" s="25"/>
+      <c r="J149" s="35"/>
+      <c r="K149" s="35"/>
+      <c r="L149" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M149" s="29"/>
+      <c r="N149" s="35"/>
       <c r="P149" s="33"/>
       <c r="R149" s="31">
         <v>0</v>
@@ -57599,22 +59300,31 @@
       <c r="B150" s="24">
         <v>1</v>
       </c>
-      <c r="C150">
-        <v>59</v>
-      </c>
-      <c r="D150">
-        <v>40</v>
-      </c>
       <c r="E150">
         <v>59</v>
       </c>
-      <c r="H150">
+      <c r="F150">
         <v>59</v>
       </c>
-      <c r="K150">
+      <c r="G150" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I150" s="28">
+        <v>40</v>
+      </c>
+      <c r="J150" s="36">
+        <v>59</v>
+      </c>
+      <c r="K150" s="36">
         <v>58</v>
       </c>
-      <c r="N150" s="25"/>
+      <c r="L150" s="35">
+        <f t="shared" si="10"/>
+        <v>41</v>
+      </c>
+      <c r="M150" s="29"/>
+      <c r="N150" s="35"/>
       <c r="P150" s="33"/>
       <c r="R150" s="31">
         <v>0</v>
@@ -58061,19 +59771,29 @@
       <c r="B151" s="24">
         <v>0.41</v>
       </c>
-      <c r="C151">
+      <c r="E151">
         <v>40</v>
       </c>
-      <c r="E151">
+      <c r="F151">
+        <v>44</v>
+      </c>
+      <c r="G151" s="31">
+        <f t="shared" si="9"/>
+        <v>-4</v>
+      </c>
+      <c r="I151" s="25"/>
+      <c r="J151" s="36">
         <v>10</v>
       </c>
-      <c r="H151">
-        <v>44</v>
-      </c>
-      <c r="K151">
+      <c r="K151" s="36">
         <v>19</v>
       </c>
-      <c r="N151" s="28">
+      <c r="L151" s="35">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="M151" s="29"/>
+      <c r="N151" s="36">
         <v>210</v>
       </c>
       <c r="O151">
@@ -58564,13 +60284,25 @@
       <c r="B152" s="24">
         <v>1</v>
       </c>
-      <c r="C152">
+      <c r="E152">
         <v>25</v>
       </c>
-      <c r="H152">
+      <c r="F152">
         <v>25</v>
       </c>
-      <c r="N152" s="28">
+      <c r="G152" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I152" s="25"/>
+      <c r="J152" s="35"/>
+      <c r="K152" s="35"/>
+      <c r="L152" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M152" s="29"/>
+      <c r="N152" s="36">
         <v>154</v>
       </c>
       <c r="O152">
@@ -59051,7 +60783,19 @@
       <c r="B153" s="24">
         <v>0.35</v>
       </c>
-      <c r="N153" s="28">
+      <c r="G153" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I153" s="25"/>
+      <c r="J153" s="35"/>
+      <c r="K153" s="35"/>
+      <c r="L153" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M153" s="29"/>
+      <c r="N153" s="36">
         <v>120</v>
       </c>
       <c r="O153">
@@ -59457,7 +61201,19 @@
       <c r="B154" s="24">
         <v>1</v>
       </c>
-      <c r="N154" s="28">
+      <c r="G154" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I154" s="25"/>
+      <c r="J154" s="35"/>
+      <c r="K154" s="35"/>
+      <c r="L154" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M154" s="29"/>
+      <c r="N154" s="36">
         <v>62</v>
       </c>
       <c r="O154">
@@ -59861,7 +61617,19 @@
       <c r="B155" s="24">
         <v>0.4</v>
       </c>
-      <c r="N155" s="25"/>
+      <c r="G155" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I155" s="25"/>
+      <c r="J155" s="35"/>
+      <c r="K155" s="35"/>
+      <c r="L155" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M155" s="29"/>
+      <c r="N155" s="35"/>
       <c r="P155" s="33"/>
       <c r="R155" s="31">
         <v>0</v>
@@ -60290,19 +62058,29 @@
       <c r="B156" s="24">
         <v>0.41</v>
       </c>
-      <c r="C156">
+      <c r="E156">
         <v>110</v>
       </c>
-      <c r="E156">
+      <c r="F156">
+        <v>113</v>
+      </c>
+      <c r="G156" s="31">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="I156" s="25"/>
+      <c r="J156" s="36">
         <v>40</v>
       </c>
-      <c r="H156">
-        <v>113</v>
-      </c>
-      <c r="K156">
+      <c r="K156" s="36">
         <v>49</v>
       </c>
-      <c r="N156" s="28">
+      <c r="L156" s="35">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="M156" s="29"/>
+      <c r="N156" s="36">
         <v>120</v>
       </c>
       <c r="O156">
@@ -60794,19 +62572,29 @@
       <c r="B157" s="24">
         <v>1</v>
       </c>
-      <c r="C157">
+      <c r="E157">
         <v>31</v>
       </c>
-      <c r="E157">
+      <c r="F157">
+        <v>34</v>
+      </c>
+      <c r="G157" s="31">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="I157" s="25"/>
+      <c r="J157" s="36">
         <v>12</v>
       </c>
-      <c r="H157">
-        <v>34</v>
-      </c>
-      <c r="K157">
+      <c r="K157" s="36">
         <v>14</v>
       </c>
-      <c r="N157" s="25"/>
+      <c r="L157" s="35">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="M157" s="29"/>
+      <c r="N157" s="35"/>
       <c r="P157">
         <v>13</v>
       </c>
@@ -61235,19 +63023,29 @@
       <c r="B158" s="24">
         <v>0.35</v>
       </c>
-      <c r="C158">
-        <v>60</v>
-      </c>
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="H158">
+      <c r="F158">
         <v>61</v>
       </c>
-      <c r="K158">
+      <c r="G158" s="31">
+        <f t="shared" si="9"/>
+        <v>-1</v>
+      </c>
+      <c r="I158" s="25"/>
+      <c r="J158" s="36">
         <v>60</v>
       </c>
-      <c r="N158" s="25"/>
+      <c r="K158" s="36">
+        <v>60</v>
+      </c>
+      <c r="L158" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M158" s="29"/>
+      <c r="N158" s="35"/>
       <c r="P158" s="33"/>
       <c r="R158" s="31">
         <v>0</v>
@@ -61682,7 +63480,19 @@
       <c r="B159" s="24">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N159" s="25"/>
+      <c r="G159" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I159" s="25"/>
+      <c r="J159" s="35"/>
+      <c r="K159" s="35"/>
+      <c r="L159" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M159" s="29"/>
+      <c r="N159" s="35"/>
       <c r="P159" s="33"/>
       <c r="R159" s="31">
         <v>0</v>
@@ -61920,19 +63730,29 @@
       <c r="B160" s="24">
         <v>0.18</v>
       </c>
-      <c r="C160">
-        <v>150</v>
-      </c>
       <c r="E160">
         <v>150</v>
       </c>
-      <c r="H160">
+      <c r="F160">
         <v>153</v>
       </c>
-      <c r="K160">
+      <c r="G160" s="31">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="I160" s="25"/>
+      <c r="J160" s="36">
+        <v>150</v>
+      </c>
+      <c r="K160" s="36">
         <v>154</v>
       </c>
-      <c r="N160" s="25"/>
+      <c r="L160" s="35">
+        <f t="shared" si="10"/>
+        <v>-4</v>
+      </c>
+      <c r="M160" s="29"/>
+      <c r="N160" s="35"/>
       <c r="P160" s="33"/>
       <c r="R160" s="31">
         <v>0</v>
@@ -62345,7 +64165,19 @@
       <c r="B161" s="24">
         <v>1</v>
       </c>
-      <c r="N161" s="25"/>
+      <c r="G161" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I161" s="25"/>
+      <c r="J161" s="35"/>
+      <c r="K161" s="35"/>
+      <c r="L161" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M161" s="29"/>
+      <c r="N161" s="35"/>
       <c r="P161" s="33"/>
       <c r="R161" s="31">
         <v>0</v>
@@ -62644,7 +64476,19 @@
       <c r="B162" s="24">
         <v>0.4</v>
       </c>
-      <c r="N162" s="25"/>
+      <c r="G162" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I162" s="25"/>
+      <c r="J162" s="35"/>
+      <c r="K162" s="35"/>
+      <c r="L162" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M162" s="29"/>
+      <c r="N162" s="35"/>
       <c r="P162" s="33"/>
       <c r="R162" s="31">
         <v>0</v>
@@ -62984,7 +64828,19 @@
       <c r="B163" s="24">
         <v>1</v>
       </c>
-      <c r="N163" s="25"/>
+      <c r="G163" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I163" s="25"/>
+      <c r="J163" s="35"/>
+      <c r="K163" s="35"/>
+      <c r="L163" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M163" s="29"/>
+      <c r="N163" s="35"/>
       <c r="P163" s="33"/>
       <c r="R163" s="31">
         <v>0</v>
@@ -63228,7 +65084,19 @@
       <c r="B164" s="24">
         <v>0.84</v>
       </c>
-      <c r="N164" s="25"/>
+      <c r="G164" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I164" s="25"/>
+      <c r="J164" s="35"/>
+      <c r="K164" s="35"/>
+      <c r="L164" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M164" s="29"/>
+      <c r="N164" s="35"/>
       <c r="P164" s="33"/>
       <c r="R164" s="31">
         <v>0</v>
@@ -63471,7 +65339,19 @@
       <c r="B165" s="24">
         <v>0.84</v>
       </c>
-      <c r="N165" s="25"/>
+      <c r="G165" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I165" s="25"/>
+      <c r="J165" s="35"/>
+      <c r="K165" s="35"/>
+      <c r="L165" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M165" s="29"/>
+      <c r="N165" s="35"/>
       <c r="P165" s="33"/>
       <c r="R165" s="31">
         <v>0</v>
@@ -63709,19 +65589,29 @@
       <c r="B166" s="24">
         <v>0.35</v>
       </c>
-      <c r="C166">
-        <v>144</v>
-      </c>
       <c r="E166">
         <v>144</v>
       </c>
-      <c r="H166">
+      <c r="F166">
         <v>148</v>
       </c>
-      <c r="K166">
+      <c r="G166" s="31">
+        <f t="shared" si="9"/>
+        <v>-4</v>
+      </c>
+      <c r="I166" s="25"/>
+      <c r="J166" s="36">
+        <v>144</v>
+      </c>
+      <c r="K166" s="36">
         <v>148</v>
       </c>
-      <c r="N166" s="28">
+      <c r="L166" s="35">
+        <f t="shared" si="10"/>
+        <v>-4</v>
+      </c>
+      <c r="M166" s="29"/>
+      <c r="N166" s="36">
         <v>64</v>
       </c>
       <c r="O166">
@@ -64173,19 +66063,29 @@
       <c r="B167" s="24">
         <v>1</v>
       </c>
-      <c r="C167">
+      <c r="E167">
         <v>214</v>
       </c>
-      <c r="E167">
+      <c r="F167">
+        <v>214</v>
+      </c>
+      <c r="G167" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I167" s="25"/>
+      <c r="J167" s="36">
         <v>213</v>
       </c>
-      <c r="H167">
-        <v>214</v>
-      </c>
-      <c r="K167">
+      <c r="K167" s="36">
         <v>213</v>
       </c>
-      <c r="N167" s="25"/>
+      <c r="L167" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M167" s="29"/>
+      <c r="N167" s="35"/>
       <c r="P167">
         <v>17</v>
       </c>
@@ -64670,19 +66570,29 @@
       <c r="B168" s="24">
         <v>0.35</v>
       </c>
-      <c r="C168">
-        <v>240</v>
-      </c>
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="H168">
+      <c r="F168">
         <v>247</v>
       </c>
-      <c r="K168">
+      <c r="G168" s="31">
+        <f t="shared" si="9"/>
+        <v>-7</v>
+      </c>
+      <c r="I168" s="25"/>
+      <c r="J168" s="36">
+        <v>240</v>
+      </c>
+      <c r="K168" s="36">
         <v>246</v>
       </c>
-      <c r="N168" s="25"/>
+      <c r="L168" s="35">
+        <f t="shared" si="10"/>
+        <v>-6</v>
+      </c>
+      <c r="M168" s="29"/>
+      <c r="N168" s="35"/>
       <c r="P168" s="33"/>
       <c r="R168" s="31">
         <v>0</v>
@@ -65173,7 +67083,19 @@
       <c r="B169" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N169" s="25"/>
+      <c r="G169" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I169" s="25"/>
+      <c r="J169" s="35"/>
+      <c r="K169" s="35"/>
+      <c r="L169" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M169" s="29"/>
+      <c r="N169" s="35"/>
       <c r="P169" s="33"/>
       <c r="R169" s="31">
         <v>0</v>
@@ -65432,19 +67354,29 @@
       <c r="B170" s="24">
         <v>0.3</v>
       </c>
-      <c r="C170">
-        <v>42</v>
-      </c>
       <c r="E170">
         <v>42</v>
       </c>
-      <c r="H170">
+      <c r="F170">
         <v>42</v>
       </c>
-      <c r="K170">
+      <c r="G170" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I170" s="25"/>
+      <c r="J170" s="36">
+        <v>42</v>
+      </c>
+      <c r="K170" s="36">
         <v>43</v>
       </c>
-      <c r="N170" s="25"/>
+      <c r="L170" s="35">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="M170" s="29"/>
+      <c r="N170" s="35"/>
       <c r="P170" s="33"/>
       <c r="R170" s="31">
         <v>0</v>
@@ -65775,7 +67707,19 @@
       <c r="B171" s="24">
         <v>0.18</v>
       </c>
-      <c r="N171" s="25"/>
+      <c r="G171" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I171" s="25"/>
+      <c r="J171" s="35"/>
+      <c r="K171" s="35"/>
+      <c r="L171" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M171" s="29"/>
+      <c r="N171" s="35"/>
       <c r="P171" s="33"/>
       <c r="R171" s="31">
         <v>0</v>
@@ -66045,19 +67989,29 @@
       <c r="B172" s="24">
         <v>0.3</v>
       </c>
-      <c r="C172">
+      <c r="E172">
         <v>40</v>
       </c>
-      <c r="E172">
+      <c r="F172">
+        <v>43</v>
+      </c>
+      <c r="G172" s="31">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="I172" s="25"/>
+      <c r="J172" s="36">
         <v>16</v>
       </c>
-      <c r="H172">
-        <v>43</v>
-      </c>
-      <c r="K172">
+      <c r="K172" s="36">
         <v>19</v>
       </c>
-      <c r="N172" s="28">
+      <c r="L172" s="35">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="M172" s="29"/>
+      <c r="N172" s="36">
         <v>16</v>
       </c>
       <c r="O172">
@@ -66352,19 +68306,29 @@
       <c r="B173" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C173">
-        <v>88</v>
-      </c>
       <c r="E173">
         <v>88</v>
       </c>
-      <c r="H173">
+      <c r="F173">
         <v>88</v>
       </c>
-      <c r="K173">
+      <c r="G173" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I173" s="25"/>
+      <c r="J173" s="36">
         <v>88</v>
       </c>
-      <c r="N173" s="25"/>
+      <c r="K173" s="36">
+        <v>88</v>
+      </c>
+      <c r="L173" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M173" s="29"/>
+      <c r="N173" s="35"/>
       <c r="P173">
         <v>24</v>
       </c>
@@ -66749,10 +68713,26 @@
       <c r="B174" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H174">
+      <c r="F174">
         <v>15</v>
       </c>
-      <c r="N174" s="28">
+      <c r="G174" s="34">
+        <f t="shared" si="9"/>
+        <v>-15</v>
+      </c>
+      <c r="H174" s="31">
+        <f>-1*G174*B174</f>
+        <v>4.2</v>
+      </c>
+      <c r="I174" s="25"/>
+      <c r="J174" s="35"/>
+      <c r="K174" s="35"/>
+      <c r="L174" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M174" s="29"/>
+      <c r="N174" s="36">
         <v>120</v>
       </c>
       <c r="O174">
@@ -67164,19 +69144,29 @@
       <c r="B175" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C175">
+      <c r="E175">
         <v>96</v>
       </c>
-      <c r="E175">
+      <c r="F175">
+        <v>99</v>
+      </c>
+      <c r="G175" s="31">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="I175" s="25"/>
+      <c r="J175" s="36">
         <v>40</v>
       </c>
-      <c r="H175">
-        <v>99</v>
-      </c>
-      <c r="K175">
+      <c r="K175" s="36">
         <v>42</v>
       </c>
-      <c r="N175" s="28">
+      <c r="L175" s="35">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="M175" s="29"/>
+      <c r="N175" s="36">
         <v>120</v>
       </c>
       <c r="O175">
@@ -67600,19 +69590,29 @@
       <c r="B176" s="24">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C176">
-        <v>248</v>
-      </c>
       <c r="E176">
         <v>248</v>
       </c>
-      <c r="H176">
+      <c r="F176">
         <v>252</v>
       </c>
-      <c r="K176">
+      <c r="G176" s="31">
+        <f t="shared" si="9"/>
+        <v>-4</v>
+      </c>
+      <c r="I176" s="25"/>
+      <c r="J176" s="36">
+        <v>248</v>
+      </c>
+      <c r="K176" s="36">
         <v>253</v>
       </c>
-      <c r="N176" s="28">
+      <c r="L176" s="35">
+        <f t="shared" si="10"/>
+        <v>-5</v>
+      </c>
+      <c r="M176" s="29"/>
+      <c r="N176" s="36">
         <v>16</v>
       </c>
       <c r="O176">
@@ -67992,19 +69992,29 @@
       <c r="B177" s="24">
         <v>0.4</v>
       </c>
-      <c r="C177">
+      <c r="E177">
         <v>84</v>
       </c>
-      <c r="E177">
+      <c r="F177">
+        <v>89</v>
+      </c>
+      <c r="G177" s="31">
+        <f t="shared" si="9"/>
+        <v>-5</v>
+      </c>
+      <c r="I177" s="25"/>
+      <c r="J177" s="36">
         <v>90</v>
       </c>
-      <c r="H177">
-        <v>89</v>
-      </c>
-      <c r="K177">
+      <c r="K177" s="36">
         <v>90</v>
       </c>
-      <c r="N177" s="25"/>
+      <c r="L177" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M177" s="29"/>
+      <c r="N177" s="35"/>
       <c r="P177" s="33"/>
       <c r="R177" s="31">
         <v>0</v>
@@ -68176,7 +70186,19 @@
       <c r="B178" s="24">
         <v>0.33</v>
       </c>
-      <c r="N178" s="25"/>
+      <c r="G178" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I178" s="25"/>
+      <c r="J178" s="35"/>
+      <c r="K178" s="35"/>
+      <c r="L178" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M178" s="29"/>
+      <c r="N178" s="35"/>
       <c r="P178" s="33"/>
       <c r="R178" s="31">
         <v>0</v>
@@ -68416,7 +70438,19 @@
       <c r="B179" s="24">
         <v>0.3</v>
       </c>
-      <c r="N179" s="28">
+      <c r="G179" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I179" s="25"/>
+      <c r="J179" s="35"/>
+      <c r="K179" s="35"/>
+      <c r="L179" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M179" s="29"/>
+      <c r="N179" s="36">
         <v>84</v>
       </c>
       <c r="O179">
@@ -68762,7 +70796,19 @@
       <c r="B180" s="24">
         <v>1</v>
       </c>
-      <c r="N180" s="25"/>
+      <c r="G180" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I180" s="25"/>
+      <c r="J180" s="35"/>
+      <c r="K180" s="35"/>
+      <c r="L180" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M180" s="29"/>
+      <c r="N180" s="35"/>
       <c r="P180">
         <v>19</v>
       </c>
@@ -68921,7 +70967,19 @@
       <c r="B181" s="24">
         <v>0.25</v>
       </c>
-      <c r="N181" s="25"/>
+      <c r="G181" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I181" s="25"/>
+      <c r="J181" s="35"/>
+      <c r="K181" s="35"/>
+      <c r="L181" s="35">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M181" s="29"/>
+      <c r="N181" s="35"/>
       <c r="P181" s="33"/>
       <c r="R181" s="31">
         <v>0</v>
@@ -69085,19 +71143,29 @@
       <c r="B182" s="24">
         <v>0.4</v>
       </c>
-      <c r="C182">
-        <v>24</v>
-      </c>
       <c r="E182">
         <v>24</v>
       </c>
-      <c r="H182">
+      <c r="F182">
         <v>29</v>
       </c>
-      <c r="K182">
+      <c r="G182" s="31">
+        <f t="shared" si="9"/>
+        <v>-5</v>
+      </c>
+      <c r="I182" s="25"/>
+      <c r="J182" s="36">
+        <v>24</v>
+      </c>
+      <c r="K182" s="36">
         <v>30</v>
       </c>
-      <c r="N182" s="25"/>
+      <c r="L182" s="35">
+        <f t="shared" si="10"/>
+        <v>-6</v>
+      </c>
+      <c r="M182" s="29"/>
+      <c r="N182" s="35"/>
       <c r="P182" s="33"/>
       <c r="R182" s="31">
         <v>0</v>
@@ -69261,16 +71329,30 @@
       <c r="B183" s="24">
         <v>0.12</v>
       </c>
-      <c r="E183">
+      <c r="F183">
+        <v>29</v>
+      </c>
+      <c r="G183" s="34">
+        <f t="shared" si="9"/>
+        <v>-29</v>
+      </c>
+      <c r="H183" s="31">
+        <f>-1*G183*B183</f>
+        <v>3.48</v>
+      </c>
+      <c r="I183" s="25"/>
+      <c r="J183" s="36">
         <v>8</v>
       </c>
-      <c r="H183">
-        <v>29</v>
-      </c>
-      <c r="K183">
+      <c r="K183" s="36">
         <v>13</v>
       </c>
-      <c r="N183" s="28">
+      <c r="L183" s="35">
+        <f t="shared" si="10"/>
+        <v>-5</v>
+      </c>
+      <c r="M183" s="29"/>
+      <c r="N183" s="36">
         <v>24</v>
       </c>
       <c r="O183">
@@ -69420,7 +71502,19 @@
       <c r="B184" s="24">
         <v>0.18</v>
       </c>
-      <c r="N184" s="18"/>
+      <c r="G184" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I184" s="18"/>
+      <c r="J184" s="9"/>
+      <c r="K184" s="9"/>
+      <c r="L184" s="9">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M184" s="10"/>
+      <c r="N184" s="9"/>
       <c r="O184" s="9"/>
       <c r="P184" s="8"/>
       <c r="Q184" s="9"/>
